--- a/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_35.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_35.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1728492.386273654</v>
+        <v>1720546.743957416</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7154817.030747599</v>
+        <v>7155604.990343557</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7154817.030747599</v>
+        <v>7155604.990343557</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1421810.501097731</v>
+        <v>1428532.779235607</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1421810.501097731</v>
+        <v>1428532.779235607</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18751487.34853293</v>
+        <v>18747436.7118848</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>28.70619138541446</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>92.50795918773906</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -745,13 +745,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>135.3518862151736</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -778,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
       </c>
       <c r="S3" t="n">
-        <v>367.5269961188086</v>
+        <v>66.5639999646113</v>
       </c>
       <c r="T3" t="n">
         <v>5.357765217513816</v>
@@ -848,13 +848,13 @@
         <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
-        <v>169.593904625629</v>
+        <v>171.1850752716849</v>
       </c>
       <c r="O4" t="n">
         <v>240.445564079015</v>
       </c>
       <c r="P4" t="n">
-        <v>287.4478973282775</v>
+        <v>254.8103266822216</v>
       </c>
       <c r="Q4" t="n">
         <v>325.839266425598</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>254.8621611211898</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1018,7 +1018,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>385</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
@@ -1030,10 +1030,10 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>154.4721739301591</v>
       </c>
       <c r="W6" t="n">
-        <v>32.37314290982852</v>
+        <v>385</v>
       </c>
       <c r="X6" t="n">
         <v>385</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1094,7 +1094,7 @@
         <v>287.4478973282775</v>
       </c>
       <c r="Q7" t="n">
-        <v>324.2480957795422</v>
+        <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
         <v>326.6021279811511</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>32.46356367243068</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1219,13 +1219,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>199.8180013219744</v>
       </c>
       <c r="G9" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>152.3438537259095</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>147.2737972923793</v>
@@ -1261,7 +1261,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>385</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
         <v>0.2103597601867477</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1383,7 +1383,7 @@
         <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>188.5028512606473</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>275.3413603594427</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
@@ -1565,13 +1565,13 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1611,7 +1611,7 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>184.8564821639885</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F14" t="n">
         <v>179.8896287080119</v>
@@ -1623,7 +1623,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>5.493192557119869</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>3.77112610161862</v>
@@ -1787,10 +1787,10 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1808,7 +1808,7 @@
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>60.03733452678513</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1823,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5.493192557119869</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U17" t="n">
-        <v>429.7144891057306</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V17" t="n">
         <v>404.8510241668239</v>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2039,10 +2039,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>344.5479255901462</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2088,7 +2088,7 @@
         <v>179.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>179.8896287080119</v>
+        <v>185.3828212651317</v>
       </c>
       <c r="G20" t="n">
         <v>178.7573722870162</v>
@@ -2139,7 +2139,7 @@
         <v>404.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>418.8666685380672</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X20" t="n">
         <v>367.2818334606677</v>
@@ -2261,13 +2261,13 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>46.51799792468741</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>295.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2297,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S23" t="n">
         <v>269.8481678023229</v>
@@ -2370,7 +2370,7 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U23" t="n">
-        <v>424.2212965486107</v>
+        <v>429.7144891057306</v>
       </c>
       <c r="V23" t="n">
         <v>404.8510241668239</v>
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -2483,13 +2483,13 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>210.6076238552182</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
         <v>1.372809838709685</v>
       </c>
       <c r="X25" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -2550,28 +2550,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>256.9993129555745</v>
+        <v>257.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>225.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>186.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>180.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>180.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>179.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>184.0096587035274</v>
       </c>
       <c r="I26" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2598,28 +2598,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>25.87859882829446</v>
+        <v>26.87859882829446</v>
       </c>
       <c r="S26" t="n">
-        <v>269.8481678023229</v>
+        <v>270.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>361.6755817285639</v>
+        <v>362.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>424.2212965486107</v>
+        <v>425.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>404.8510241668239</v>
+        <v>405.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>413.3734759809475</v>
+        <v>414.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>367.2818334606677</v>
+        <v>368.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>304.9762252399261</v>
       </c>
     </row>
     <row r="27">
@@ -2629,25 +2629,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>159.5565566463266</v>
+        <v>160.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>136.0999124455193</v>
+        <v>137.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>122.9376868977026</v>
+        <v>123.9376868977026</v>
       </c>
       <c r="E27" t="n">
-        <v>117.6720972219126</v>
+        <v>118.6720972219126</v>
       </c>
       <c r="F27" t="n">
-        <v>114.6362423378769</v>
+        <v>115.6362423378769</v>
       </c>
       <c r="G27" t="n">
-        <v>100.7395358750273</v>
+        <v>101.7395358750273</v>
       </c>
       <c r="H27" t="n">
-        <v>107.1680871864211</v>
+        <v>108.1680871864211</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>322.2737972923793</v>
+        <v>323.2737972923793</v>
       </c>
       <c r="S27" t="n">
-        <v>241.5639999646113</v>
+        <v>242.5639999646113</v>
       </c>
       <c r="T27" t="n">
-        <v>180.3577652175138</v>
+        <v>181.3577652175138</v>
       </c>
       <c r="U27" t="n">
-        <v>175.2103597601867</v>
+        <v>176.2103597601867</v>
       </c>
       <c r="V27" t="n">
-        <v>189.5106671915202</v>
+        <v>190.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>207.3731429098285</v>
+        <v>208.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>194.8627394453875</v>
+        <v>195.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>174.3913927661343</v>
+        <v>175.3913927661343</v>
       </c>
     </row>
     <row r="28">
@@ -2717,16 +2717,16 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>39.36197079964791</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>4.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2747,13 +2747,13 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>233.3594533926489</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>333.8762994885276</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2771,10 +2771,10 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>2.372809838709685</v>
       </c>
       <c r="X28" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>224.4745782429939</v>
+        <v>229.9677708001137</v>
       </c>
       <c r="D29" t="n">
         <v>185.3391557398498</v>
@@ -2808,7 +2808,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I29" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2951,16 +2951,16 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>3.77112610161862</v>
@@ -2993,7 +2993,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>181.772158324378</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>1.372809838709685</v>
       </c>
       <c r="X31" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G32" t="n">
-        <v>178.7573722870162</v>
+        <v>184.2505648441361</v>
       </c>
       <c r="H32" t="n">
         <v>183.0096587035274</v>
@@ -3072,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S32" t="n">
         <v>269.8481678023229</v>
@@ -3218,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>342.1496093272373</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3245,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3276,13 +3276,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>53.75737228701621</v>
+        <v>57.72276367243072</v>
       </c>
       <c r="H35" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I35" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3349,16 +3349,16 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>86.93822665041522</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>325.7395358750273</v>
+        <v>80.50967533902147</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3513,13 +3513,13 @@
         <v>54.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>57.72276367243072</v>
+        <v>53.75737228701621</v>
       </c>
       <c r="H38" t="n">
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>22.47211154361427</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
         <v>197.2737972923793</v>
@@ -3634,7 +3634,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U39" t="n">
-        <v>112.8881222856293</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V39" t="n">
         <v>64.51066719152016</v>
@@ -3646,7 +3646,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3753,7 +3753,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H41" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T41" t="n">
         <v>236.6755817285639</v>
@@ -3817,7 +3817,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>73.77767497096173</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
         <v>547.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T42" t="n">
         <v>55.35776521751382</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>131.9993129555745</v>
+        <v>132.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>99.47457824299391</v>
+        <v>100.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>60.33915573984979</v>
+        <v>61.33915573984979</v>
       </c>
       <c r="E44" t="n">
-        <v>54.36328960686865</v>
+        <v>55.36328960686865</v>
       </c>
       <c r="F44" t="n">
-        <v>58.85502009342638</v>
+        <v>55.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>53.75737228701621</v>
+        <v>44.7227636724308</v>
       </c>
       <c r="H44" t="n">
-        <v>58.00965870352741</v>
+        <v>59.00965870352741</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4023,25 +4023,25 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>144.8481678023229</v>
+        <v>145.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>236.6755817285639</v>
+        <v>237.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>299.2212965486107</v>
+        <v>300.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>279.8510241668239</v>
+        <v>280.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>288.3734759809475</v>
+        <v>289.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>242.2818334606677</v>
+        <v>243.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>161.3174326828064</v>
+        <v>162.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4051,10 +4051,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>34.55655664632661</v>
+        <v>35.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>91.60958778454074</v>
+        <v>12.09991244551929</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4069,7 +4069,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4099,28 +4099,28 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>116.5639999646113</v>
+        <v>171.2417624900538</v>
       </c>
       <c r="T45" t="n">
-        <v>55.35776521751382</v>
+        <v>56.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>50.21035976018675</v>
+        <v>51.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>64.51066719152016</v>
+        <v>65.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>82.37314290982852</v>
+        <v>83.37314290982852</v>
       </c>
       <c r="X45" t="n">
-        <v>69.86273944538755</v>
+        <v>70.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>49.39139276613435</v>
+        <v>50.39139276613435</v>
       </c>
     </row>
     <row r="46">
@@ -4160,28 +4160,28 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>73.54762815777917</v>
+        <v>74.54762815777917</v>
       </c>
       <c r="M46" t="n">
-        <v>170.6316114025499</v>
+        <v>171.6316114025499</v>
       </c>
       <c r="N46" t="n">
-        <v>221.1850752716849</v>
+        <v>222.1850752716849</v>
       </c>
       <c r="O46" t="n">
-        <v>290.445564079015</v>
+        <v>291.445564079015</v>
       </c>
       <c r="P46" t="n">
-        <v>337.4478973282775</v>
+        <v>338.4478973282775</v>
       </c>
       <c r="Q46" t="n">
-        <v>375.839266425598</v>
+        <v>374.1648209739382</v>
       </c>
       <c r="R46" t="n">
-        <v>376.6021279811511</v>
+        <v>377.6021279811511</v>
       </c>
       <c r="S46" t="n">
-        <v>12.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>141.4463380542246</v>
+        <v>111.8101851396645</v>
       </c>
       <c r="C2" t="n">
-        <v>91.47201659665494</v>
+        <v>61.83586368209485</v>
       </c>
       <c r="D2" t="n">
-        <v>81.02842494024101</v>
+        <v>51.39227202568092</v>
       </c>
       <c r="E2" t="n">
-        <v>76.62106170097975</v>
+        <v>46.98490878641967</v>
       </c>
       <c r="F2" t="n">
-        <v>71.68204280399807</v>
+        <v>42.04588988943799</v>
       </c>
       <c r="G2" t="n">
-        <v>67.88671726155745</v>
+        <v>38.25056434699738</v>
       </c>
       <c r="H2" t="n">
-        <v>59.79615291456007</v>
+        <v>30.16</v>
       </c>
       <c r="I2" t="n">
-        <v>30.8</v>
+        <v>30.16</v>
       </c>
       <c r="J2" t="n">
-        <v>411.95</v>
+        <v>30.16</v>
       </c>
       <c r="K2" t="n">
-        <v>411.95</v>
+        <v>30.16</v>
       </c>
       <c r="L2" t="n">
-        <v>411.95</v>
+        <v>30.16</v>
       </c>
       <c r="M2" t="n">
-        <v>411.95</v>
+        <v>403.39</v>
       </c>
       <c r="N2" t="n">
-        <v>411.95</v>
+        <v>776.6200000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>793.1</v>
+        <v>1149.85</v>
       </c>
       <c r="P2" t="n">
-        <v>1158.85</v>
+        <v>1149.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>1540</v>
+        <v>1508</v>
       </c>
       <c r="R2" t="n">
-        <v>1540</v>
+        <v>1508.000000000002</v>
       </c>
       <c r="S2" t="n">
-        <v>1444.193769896644</v>
+        <v>1414.557616982083</v>
       </c>
       <c r="T2" t="n">
-        <v>1255.632576231427</v>
+        <v>1225.996423316867</v>
       </c>
       <c r="U2" t="n">
-        <v>1003.893892848992</v>
+        <v>974.2577399344323</v>
       </c>
       <c r="V2" t="n">
-        <v>771.7211411653319</v>
+        <v>742.0849882507717</v>
       </c>
       <c r="W2" t="n">
-        <v>530.9398522956878</v>
+        <v>501.3036993811277</v>
       </c>
       <c r="X2" t="n">
-        <v>336.7157780929932</v>
+        <v>307.079625178433</v>
       </c>
       <c r="Y2" t="n">
-        <v>224.2739268982392</v>
+        <v>194.6377739836791</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>593.1864931608338</v>
+        <v>721.7219790837811</v>
       </c>
       <c r="C3" t="n">
-        <v>593.1864931608338</v>
+        <v>721.7219790837811</v>
       </c>
       <c r="D3" t="n">
-        <v>593.1864931608338</v>
+        <v>721.7219790837811</v>
       </c>
       <c r="E3" t="n">
-        <v>593.1864931608338</v>
+        <v>721.7219790837811</v>
       </c>
       <c r="F3" t="n">
-        <v>250.1195817084329</v>
+        <v>585.0029020987572</v>
       </c>
       <c r="G3" t="n">
-        <v>250.1195817084329</v>
+        <v>585.0029020987572</v>
       </c>
       <c r="H3" t="n">
-        <v>250.1195817084329</v>
+        <v>249.4795817084329</v>
       </c>
       <c r="I3" t="n">
-        <v>30.8</v>
+        <v>30.16</v>
       </c>
       <c r="J3" t="n">
-        <v>154.756520175299</v>
+        <v>154.1165201752989</v>
       </c>
       <c r="K3" t="n">
-        <v>343.9493362696824</v>
+        <v>343.3093362696824</v>
       </c>
       <c r="L3" t="n">
-        <v>615.2997978648825</v>
+        <v>614.6597978648824</v>
       </c>
       <c r="M3" t="n">
-        <v>701.3803396077418</v>
+        <v>700.7403396077417</v>
       </c>
       <c r="N3" t="n">
-        <v>834.6606242153101</v>
+        <v>834.02062421531</v>
       </c>
       <c r="O3" t="n">
-        <v>1073.703075899029</v>
+        <v>1073.063075899029</v>
       </c>
       <c r="P3" t="n">
-        <v>1186.232420368536</v>
+        <v>1185.592420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1186.232420368536</v>
+        <v>1010.764879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1037.471008962092</v>
+        <v>862.003468466658</v>
       </c>
       <c r="S3" t="n">
-        <v>666.2316189430933</v>
+        <v>794.7671048660405</v>
       </c>
       <c r="T3" t="n">
-        <v>660.8197348849985</v>
+        <v>789.3552208079458</v>
       </c>
       <c r="U3" t="n">
-        <v>660.6072502787492</v>
+        <v>789.1427362016965</v>
       </c>
       <c r="V3" t="n">
-        <v>645.9500106913551</v>
+        <v>774.4854966143024</v>
       </c>
       <c r="W3" t="n">
-        <v>613.249866337993</v>
+        <v>741.7853522609403</v>
       </c>
       <c r="X3" t="n">
-        <v>593.1864931608338</v>
+        <v>721.7219790837811</v>
       </c>
       <c r="Y3" t="n">
-        <v>593.1864931608338</v>
+        <v>721.7219790837811</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>775.7097405151412</v>
+        <v>330.1983837846587</v>
       </c>
       <c r="C4" t="n">
-        <v>901.711746333577</v>
+        <v>456.2003896030945</v>
       </c>
       <c r="D4" t="n">
-        <v>901.711746333577</v>
+        <v>569.5195337280946</v>
       </c>
       <c r="E4" t="n">
-        <v>1019.54065054499</v>
+        <v>687.3484379395077</v>
       </c>
       <c r="F4" t="n">
-        <v>1143.901623136926</v>
+        <v>811.7094105314432</v>
       </c>
       <c r="G4" t="n">
-        <v>1143.901623136926</v>
+        <v>965.1159764183284</v>
       </c>
       <c r="H4" t="n">
-        <v>1313.418208296323</v>
+        <v>1134.632561577726</v>
       </c>
       <c r="I4" t="n">
-        <v>1313.418208296323</v>
+        <v>1134.632561577726</v>
       </c>
       <c r="J4" t="n">
-        <v>1429.635566063132</v>
+        <v>1495.716302230177</v>
       </c>
       <c r="K4" t="n">
-        <v>1540</v>
+        <v>1508</v>
       </c>
       <c r="L4" t="n">
-        <v>1516.214517012344</v>
+        <v>1484.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1394.364404484516</v>
+        <v>1362.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1189.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>946.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>689.1917115219688</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.7011393749001</v>
+        <v>360.0611393749001</v>
       </c>
       <c r="R4" t="n">
-        <v>30.8</v>
+        <v>30.16</v>
       </c>
       <c r="S4" t="n">
-        <v>30.8</v>
+        <v>67.41025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>30.8</v>
+        <v>67.41025509417312</v>
       </c>
       <c r="U4" t="n">
-        <v>30.8</v>
+        <v>67.41025509417312</v>
       </c>
       <c r="V4" t="n">
-        <v>229.621392885946</v>
+        <v>67.41025509417312</v>
       </c>
       <c r="W4" t="n">
-        <v>401.5123111456234</v>
+        <v>67.41025509417312</v>
       </c>
       <c r="X4" t="n">
-        <v>552.5431021698168</v>
+        <v>218.4410461183666</v>
       </c>
       <c r="Y4" t="n">
-        <v>663.9524028488491</v>
+        <v>218.4410461183666</v>
       </c>
     </row>
     <row r="5">
@@ -4564,19 +4564,19 @@
         <v>411.9499999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>793.0999999999999</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>793.1</v>
+        <v>1158.85</v>
       </c>
       <c r="N5" t="n">
-        <v>1174.25</v>
+        <v>1540</v>
       </c>
       <c r="O5" t="n">
-        <v>1174.25</v>
+        <v>1540</v>
       </c>
       <c r="P5" t="n">
-        <v>1174.25</v>
+        <v>1540</v>
       </c>
       <c r="Q5" t="n">
         <v>1540</v>
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>288.2365263850402</v>
+        <v>30.8</v>
       </c>
       <c r="C6" t="n">
-        <v>288.2365263850402</v>
+        <v>30.8</v>
       </c>
       <c r="D6" t="n">
-        <v>288.2365263850402</v>
+        <v>30.8</v>
       </c>
       <c r="E6" t="n">
-        <v>288.2365263850402</v>
+        <v>30.8</v>
       </c>
       <c r="F6" t="n">
-        <v>288.2365263850402</v>
+        <v>30.8</v>
       </c>
       <c r="G6" t="n">
-        <v>288.2365263850402</v>
+        <v>30.8</v>
       </c>
       <c r="H6" t="n">
         <v>30.8</v>
@@ -4661,28 +4661,28 @@
         <v>1186.232420368536</v>
       </c>
       <c r="R6" t="n">
-        <v>797.3435314796468</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S6" t="n">
-        <v>730.1071678790294</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T6" t="n">
-        <v>724.6952838209346</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U6" t="n">
-        <v>724.4827992146853</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V6" t="n">
-        <v>709.8255596272912</v>
+        <v>808.5777777777778</v>
       </c>
       <c r="W6" t="n">
-        <v>677.1254152739291</v>
+        <v>419.6888888888889</v>
       </c>
       <c r="X6" t="n">
-        <v>288.2365263850402</v>
+        <v>30.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>288.2365263850402</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="7">
@@ -4692,49 +4692,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>537.7680860777841</v>
+        <v>1247.586867406406</v>
       </c>
       <c r="C7" t="n">
-        <v>663.7700918962199</v>
+        <v>1373.588873224842</v>
       </c>
       <c r="D7" t="n">
-        <v>761.2185634888302</v>
+        <v>1486.908017349842</v>
       </c>
       <c r="E7" t="n">
-        <v>761.2185634888302</v>
+        <v>1486.908017349842</v>
       </c>
       <c r="F7" t="n">
-        <v>885.5795360807657</v>
+        <v>1540</v>
       </c>
       <c r="G7" t="n">
-        <v>1038.986101967651</v>
+        <v>1540</v>
       </c>
       <c r="H7" t="n">
-        <v>1208.502687127049</v>
+        <v>1540</v>
       </c>
       <c r="I7" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="J7" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
       </c>
       <c r="L7" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M7" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N7" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O7" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P7" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q7" t="n">
         <v>360.7011393749001</v>
@@ -4746,22 +4746,22 @@
         <v>68.05025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>68.05025509417312</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>314.6014477324597</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V7" t="n">
-        <v>314.6014477324597</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="W7" t="n">
-        <v>314.6014477324597</v>
+        <v>873.3894380368879</v>
       </c>
       <c r="X7" t="n">
-        <v>314.6014477324597</v>
+        <v>1024.420229061081</v>
       </c>
       <c r="Y7" t="n">
-        <v>426.010748411492</v>
+        <v>1135.829529740114</v>
       </c>
     </row>
     <row r="8">
@@ -4786,34 +4786,34 @@
         <v>71.68204280399807</v>
       </c>
       <c r="G8" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H8" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I8" t="n">
         <v>30.8</v>
       </c>
       <c r="J8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="M8" t="n">
         <v>411.95</v>
       </c>
-      <c r="K8" t="n">
-        <v>411.95</v>
-      </c>
-      <c r="L8" t="n">
-        <v>411.95</v>
-      </c>
-      <c r="M8" t="n">
-        <v>793.1</v>
-      </c>
       <c r="N8" t="n">
-        <v>1174.25</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>1174.25</v>
+        <v>1158.85</v>
       </c>
       <c r="P8" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="Q8" t="n">
         <v>1540</v>
@@ -4850,22 +4850,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
       <c r="C9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
       <c r="D9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
       <c r="E9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
       <c r="F9" t="n">
-        <v>359.8298342171994</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="G9" t="n">
-        <v>30.8</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H9" t="n">
         <v>30.8</v>
@@ -4895,31 +4895,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1032.349739837314</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>883.5883284308703</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S9" t="n">
-        <v>816.3519648302529</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T9" t="n">
-        <v>427.463075941364</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U9" t="n">
-        <v>427.2505913351147</v>
+        <v>964.6102766971304</v>
       </c>
       <c r="V9" t="n">
-        <v>412.5933517477206</v>
+        <v>949.9530371097363</v>
       </c>
       <c r="W9" t="n">
-        <v>379.8932073943585</v>
+        <v>917.2528927563742</v>
       </c>
       <c r="X9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
       <c r="Y9" t="n">
-        <v>359.8298342171994</v>
+        <v>897.189519579215</v>
       </c>
     </row>
     <row r="10">
@@ -4929,22 +4929,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>963.9386114804363</v>
+        <v>1210.336612312233</v>
       </c>
       <c r="C10" t="n">
-        <v>1089.940617298872</v>
+        <v>1336.338618130668</v>
       </c>
       <c r="D10" t="n">
-        <v>1203.259761423872</v>
+        <v>1449.657762255669</v>
       </c>
       <c r="E10" t="n">
-        <v>1321.088665635285</v>
+        <v>1540</v>
       </c>
       <c r="F10" t="n">
-        <v>1445.44963822722</v>
+        <v>1540</v>
       </c>
       <c r="G10" t="n">
-        <v>1445.44963822722</v>
+        <v>1540</v>
       </c>
       <c r="H10" t="n">
         <v>1540</v>
@@ -4959,46 +4959,46 @@
         <v>1540</v>
       </c>
       <c r="L10" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M10" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P10" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R10" t="n">
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>256.125934252978</v>
+        <v>218.8756791588049</v>
       </c>
       <c r="U10" t="n">
-        <v>502.6771268912646</v>
+        <v>465.4268717970915</v>
       </c>
       <c r="V10" t="n">
-        <v>701.4985197772105</v>
+        <v>664.2482646830374</v>
       </c>
       <c r="W10" t="n">
-        <v>701.4985197772105</v>
+        <v>836.1391829427148</v>
       </c>
       <c r="X10" t="n">
-        <v>852.529310801404</v>
+        <v>987.1699739669083</v>
       </c>
       <c r="Y10" t="n">
-        <v>963.9386114804363</v>
+        <v>1098.579274645941</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C11" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D11" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E11" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F11" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G11" t="n">
-        <v>266.2182411146742</v>
+        <v>271.7669204653003</v>
       </c>
       <c r="H11" t="n">
         <v>81.36</v>
@@ -5032,22 +5032,22 @@
         <v>81.36</v>
       </c>
       <c r="J11" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K11" t="n">
-        <v>645.2597178520556</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="L11" t="n">
-        <v>1552.289212421678</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M11" t="n">
-        <v>2063.138041150613</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="N11" t="n">
-        <v>2676.358360925376</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="O11" t="n">
-        <v>3629.400904947332</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P11" t="n">
         <v>3629.400904947332</v>
@@ -5059,25 +5059,25 @@
         <v>4041.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T11" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U11" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V11" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W11" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X11" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y11" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="12">
@@ -5114,19 +5114,19 @@
         <v>435.8613981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>643.9799167834981</v>
+        <v>847.8042142372474</v>
       </c>
       <c r="L12" t="n">
-        <v>1138.080378378698</v>
+        <v>1341.904675832448</v>
       </c>
       <c r="M12" t="n">
-        <v>1446.910920121557</v>
+        <v>1650.735217575307</v>
       </c>
       <c r="N12" t="n">
-        <v>1802.941204729126</v>
+        <v>2006.765502182875</v>
       </c>
       <c r="O12" t="n">
-        <v>2264.733656412845</v>
+        <v>2468.557953866594</v>
       </c>
       <c r="P12" t="n">
         <v>2600.013000882351</v>
@@ -5208,10 +5208,10 @@
         <v>425.5789893823512</v>
       </c>
       <c r="P13" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q13" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R13" t="n">
         <v>81.36</v>
@@ -5254,37 +5254,37 @@
         <v>815.2116584470142</v>
       </c>
       <c r="E14" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F14" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G14" t="n">
-        <v>266.2182411146742</v>
+        <v>271.7669204653003</v>
       </c>
       <c r="H14" t="n">
-        <v>81.36</v>
+        <v>86.90867935062613</v>
       </c>
       <c r="I14" t="n">
         <v>81.36</v>
       </c>
       <c r="J14" t="n">
-        <v>81.36</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="K14" t="n">
-        <v>791.0663663478683</v>
+        <v>472.6691130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>1698.095860917491</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M14" t="n">
-        <v>2208.944689646426</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="N14" t="n">
-        <v>2822.165009421189</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="O14" t="n">
-        <v>2822.165009421189</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P14" t="n">
         <v>3629.400904947332</v>
@@ -5348,13 +5348,13 @@
         <v>89.15487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>435.8613981428639</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K15" t="n">
-        <v>847.8042142372474</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L15" t="n">
-        <v>1341.904675832448</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M15" t="n">
         <v>1446.910920121557</v>
@@ -5403,52 +5403,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C16" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D16" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E16" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F16" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G16" t="n">
-        <v>174.8119284794718</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H16" t="n">
-        <v>171.0027101950085</v>
+        <v>189.862369793817</v>
       </c>
       <c r="I16" t="n">
-        <v>218.8855891310914</v>
+        <v>237.7452487298999</v>
       </c>
       <c r="J16" t="n">
-        <v>406.7193297835428</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="K16" t="n">
-        <v>342.5569320046104</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="L16" t="n">
-        <v>142.0037722492779</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="M16" t="n">
-        <v>142.0037722492779</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="N16" t="n">
-        <v>142.0037722492779</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="O16" t="n">
-        <v>142.0037722492779</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="P16" t="n">
-        <v>142.0037722492779</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q16" t="n">
-        <v>142.0037722492779</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R16" t="n">
         <v>81.36</v>
@@ -5466,13 +5466,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W16" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X16" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y16" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="17">
@@ -5482,46 +5482,46 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C17" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D17" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E17" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F17" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G17" t="n">
-        <v>266.2182411146742</v>
+        <v>271.7669204653003</v>
       </c>
       <c r="H17" t="n">
-        <v>81.36</v>
+        <v>86.90867935062613</v>
       </c>
       <c r="I17" t="n">
         <v>81.36</v>
       </c>
       <c r="J17" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K17" t="n">
-        <v>1182.375479385524</v>
+        <v>645.2597178520556</v>
       </c>
       <c r="L17" t="n">
-        <v>2089.404973955146</v>
+        <v>1552.289212421678</v>
       </c>
       <c r="M17" t="n">
-        <v>2600.253802684082</v>
+        <v>2063.138041150613</v>
       </c>
       <c r="N17" t="n">
-        <v>3213.474122458845</v>
+        <v>2676.358360925376</v>
       </c>
       <c r="O17" t="n">
-        <v>3213.474122458845</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="P17" t="n">
         <v>3629.400904947332</v>
@@ -5539,19 +5539,19 @@
         <v>3403.957223879615</v>
       </c>
       <c r="U17" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V17" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W17" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X17" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y17" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="18">
@@ -5588,10 +5588,10 @@
         <v>435.8613981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>847.8042142372474</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L18" t="n">
-        <v>1341.904675832448</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M18" t="n">
         <v>1446.910920121557</v>
@@ -5658,31 +5658,31 @@
         <v>193.6715880782802</v>
       </c>
       <c r="H19" t="n">
-        <v>193.6715880782802</v>
+        <v>189.862369793817</v>
       </c>
       <c r="I19" t="n">
-        <v>241.5544670143631</v>
+        <v>237.7452487298999</v>
       </c>
       <c r="J19" t="n">
-        <v>429.3882076668144</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="K19" t="n">
-        <v>429.3882076668144</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="L19" t="n">
-        <v>429.3882076668144</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="M19" t="n">
-        <v>429.3882076668144</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="N19" t="n">
-        <v>429.3882076668144</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="O19" t="n">
-        <v>429.3882076668144</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="P19" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q19" t="n">
         <v>81.36</v>
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C20" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D20" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E20" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F20" t="n">
         <v>446.7812434247916</v>
@@ -5752,10 +5752,10 @@
         <v>1379.698607607278</v>
       </c>
       <c r="M20" t="n">
-        <v>1379.698607607278</v>
+        <v>1890.547436336213</v>
       </c>
       <c r="N20" t="n">
-        <v>1992.918927382041</v>
+        <v>2503.767756110976</v>
       </c>
       <c r="O20" t="n">
         <v>2767.812941040225</v>
@@ -5782,13 +5782,13 @@
         <v>2566.510435278165</v>
       </c>
       <c r="W20" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X20" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y20" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="21">
@@ -5819,10 +5819,10 @@
         <v>81.36</v>
       </c>
       <c r="I21" t="n">
-        <v>81.36</v>
+        <v>89.15487796756496</v>
       </c>
       <c r="J21" t="n">
-        <v>428.066520175299</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K21" t="n">
         <v>643.9799167834981</v>
@@ -5877,52 +5877,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H22" t="n">
-        <v>191.2490463985742</v>
+        <v>189.862369793817</v>
       </c>
       <c r="I22" t="n">
-        <v>239.1319253346571</v>
+        <v>237.7452487298999</v>
       </c>
       <c r="J22" t="n">
-        <v>426.9656659871084</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="K22" t="n">
-        <v>379.977789295505</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="L22" t="n">
-        <v>379.977789295505</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="M22" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="N22" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="O22" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="P22" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q22" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R22" t="n">
         <v>81.36</v>
@@ -5940,13 +5940,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y22" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="23">
@@ -5986,13 +5986,13 @@
         <v>472.6691130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>1379.698607607278</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M23" t="n">
-        <v>1890.547436336213</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="N23" t="n">
-        <v>1890.547436336213</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="O23" t="n">
         <v>2767.812941040225</v>
@@ -6004,13 +6004,13 @@
         <v>4068</v>
       </c>
       <c r="R23" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S23" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T23" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U23" t="n">
         <v>2969.902184378877</v>
@@ -6062,13 +6062,13 @@
         <v>435.8613981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>847.8042142372474</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L24" t="n">
-        <v>1341.904675832448</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M24" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N24" t="n">
         <v>1802.941204729126</v>
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>131.2416726946888</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C25" t="n">
-        <v>131.2416726946888</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D25" t="n">
-        <v>131.2416726946888</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E25" t="n">
-        <v>131.2416726946888</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F25" t="n">
+        <v>193.6715880782802</v>
+      </c>
+      <c r="G25" t="n">
+        <v>193.6715880782802</v>
+      </c>
+      <c r="H25" t="n">
+        <v>189.862369793817</v>
+      </c>
+      <c r="I25" t="n">
+        <v>237.7452487298999</v>
+      </c>
+      <c r="J25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="K25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="L25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="M25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="N25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="O25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="P25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="R25" t="n">
         <v>81.36</v>
       </c>
-      <c r="G25" t="n">
+      <c r="S25" t="n">
         <v>81.36</v>
       </c>
-      <c r="H25" t="n">
-        <v>81.36</v>
-      </c>
-      <c r="I25" t="n">
-        <v>129.2428789360829</v>
-      </c>
-      <c r="J25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="K25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="L25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="M25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="N25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="O25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="P25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="R25" t="n">
-        <v>104.3416459974048</v>
-      </c>
-      <c r="S25" t="n">
-        <v>104.3416459974048</v>
-      </c>
       <c r="T25" t="n">
-        <v>119.1673251562096</v>
+        <v>96.18567915880486</v>
       </c>
       <c r="U25" t="n">
-        <v>192.4685177944963</v>
+        <v>169.4868717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>218.0399106804423</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="W25" t="n">
-        <v>216.653234075685</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X25" t="n">
-        <v>193.9828851563844</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y25" t="n">
-        <v>193.9828851563844</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1229.164925096351</v>
+        <v>1230.236851806331</v>
       </c>
       <c r="C26" t="n">
-        <v>1002.422926871105</v>
+        <v>1002.484752570984</v>
       </c>
       <c r="D26" t="n">
-        <v>815.2116584470142</v>
+        <v>814.2633831367921</v>
       </c>
       <c r="E26" t="n">
-        <v>634.0366184400762</v>
+        <v>632.078242119753</v>
       </c>
       <c r="F26" t="n">
-        <v>452.3299227754177</v>
+        <v>449.3614454449936</v>
       </c>
       <c r="G26" t="n">
-        <v>271.7669204653003</v>
+        <v>267.7883421247752</v>
       </c>
       <c r="H26" t="n">
-        <v>86.90867935062613</v>
+        <v>81.92</v>
       </c>
       <c r="I26" t="n">
-        <v>81.36</v>
+        <v>81.92</v>
       </c>
       <c r="J26" t="n">
-        <v>472.6691130376557</v>
+        <v>473.2291130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>1182.375479385524</v>
+        <v>1182.935479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>2089.404973955146</v>
+        <v>1182.935479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>2600.253802684082</v>
+        <v>1693.784308114459</v>
       </c>
       <c r="N26" t="n">
-        <v>3213.474122458845</v>
+        <v>2307.004627889222</v>
       </c>
       <c r="O26" t="n">
-        <v>4068</v>
+        <v>3234.412036092893</v>
       </c>
       <c r="P26" t="n">
-        <v>4068</v>
+        <v>4096</v>
       </c>
       <c r="Q26" t="n">
-        <v>4068</v>
+        <v>4096</v>
       </c>
       <c r="R26" t="n">
-        <v>4041.860001183541</v>
+        <v>4068.84990017344</v>
       </c>
       <c r="S26" t="n">
-        <v>3769.286094312508</v>
+        <v>3795.265892292306</v>
       </c>
       <c r="T26" t="n">
-        <v>3403.957223879615</v>
+        <v>3428.926920849312</v>
       </c>
       <c r="U26" t="n">
-        <v>2975.450863729503</v>
+        <v>2999.410459689099</v>
       </c>
       <c r="V26" t="n">
-        <v>2566.510435278165</v>
+        <v>2589.459930227661</v>
       </c>
       <c r="W26" t="n">
-        <v>2148.961469640845</v>
+        <v>2170.900863580239</v>
       </c>
       <c r="X26" t="n">
-        <v>1777.969718670473</v>
+        <v>1798.899011599766</v>
       </c>
       <c r="Y26" t="n">
-        <v>1488.760190708043</v>
+        <v>1490.842218428124</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>787.6767292570302</v>
+        <v>794.2973353176363</v>
       </c>
       <c r="C27" t="n">
-        <v>650.2020702211521</v>
+        <v>655.8125752716572</v>
       </c>
       <c r="D27" t="n">
-        <v>526.022588506301</v>
+        <v>530.6229925467051</v>
       </c>
       <c r="E27" t="n">
-        <v>407.1618842417428</v>
+        <v>410.7521872720458</v>
       </c>
       <c r="F27" t="n">
-        <v>291.3677000620692</v>
+        <v>293.9479020822712</v>
       </c>
       <c r="G27" t="n">
-        <v>189.6105931175971</v>
+        <v>191.1806941276981</v>
       </c>
       <c r="H27" t="n">
-        <v>81.36</v>
+        <v>81.92</v>
       </c>
       <c r="I27" t="n">
-        <v>81.36</v>
+        <v>88.72487796756495</v>
       </c>
       <c r="J27" t="n">
-        <v>232.0371006891147</v>
+        <v>434.4413981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>643.9799167834981</v>
+        <v>845.3942142372473</v>
       </c>
       <c r="L27" t="n">
-        <v>1138.080378378698</v>
+        <v>1338.504675832447</v>
       </c>
       <c r="M27" t="n">
-        <v>1446.910920121557</v>
+        <v>1646.345217575307</v>
       </c>
       <c r="N27" t="n">
-        <v>1802.941204729126</v>
+        <v>2001.385502182875</v>
       </c>
       <c r="O27" t="n">
-        <v>2264.733656412845</v>
+        <v>2282.42517156436</v>
       </c>
       <c r="P27" t="n">
-        <v>2600.013000882351</v>
+        <v>2616.714516033866</v>
       </c>
       <c r="Q27" t="n">
-        <v>2651.414528442776</v>
+        <v>2667.126043594291</v>
       </c>
       <c r="R27" t="n">
-        <v>2325.885440268656</v>
+        <v>2340.58685441007</v>
       </c>
       <c r="S27" t="n">
-        <v>2081.881399900361</v>
+        <v>2095.572713031675</v>
       </c>
       <c r="T27" t="n">
-        <v>1899.70183907459</v>
+        <v>1912.383051195802</v>
       </c>
       <c r="U27" t="n">
-        <v>1722.721677700664</v>
+        <v>1734.392788811775</v>
       </c>
       <c r="V27" t="n">
-        <v>1531.296761345593</v>
+        <v>1541.957771446603</v>
       </c>
       <c r="W27" t="n">
-        <v>1321.828940224554</v>
+        <v>1331.479849315463</v>
       </c>
       <c r="X27" t="n">
-        <v>1124.997890279718</v>
+        <v>1133.638698360526</v>
       </c>
       <c r="Y27" t="n">
-        <v>948.8449682937237</v>
+        <v>956.4756753644309</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>171.0012391589796</v>
+        <v>190.2514870681792</v>
       </c>
       <c r="C28" t="n">
-        <v>171.0012391589796</v>
+        <v>190.2514870681792</v>
       </c>
       <c r="D28" t="n">
-        <v>171.0012391589796</v>
+        <v>190.2514870681792</v>
       </c>
       <c r="E28" t="n">
-        <v>131.2416726946888</v>
+        <v>190.2514870681792</v>
       </c>
       <c r="F28" t="n">
-        <v>81.36</v>
+        <v>190.2514870681792</v>
       </c>
       <c r="G28" t="n">
-        <v>81.36</v>
+        <v>190.2514870681792</v>
       </c>
       <c r="H28" t="n">
-        <v>81.36</v>
+        <v>185.4321677736149</v>
       </c>
       <c r="I28" t="n">
-        <v>129.2428789360829</v>
+        <v>232.3250467096979</v>
       </c>
       <c r="J28" t="n">
-        <v>317.0766195885342</v>
+        <v>419.1687873621491</v>
       </c>
       <c r="K28" t="n">
-        <v>317.0766195885342</v>
+        <v>419.1687873621491</v>
       </c>
       <c r="L28" t="n">
-        <v>317.0766195885342</v>
+        <v>419.1687873621491</v>
       </c>
       <c r="M28" t="n">
-        <v>317.0766195885342</v>
+        <v>419.1687873621491</v>
       </c>
       <c r="N28" t="n">
-        <v>317.0766195885342</v>
+        <v>419.1687873621491</v>
       </c>
       <c r="O28" t="n">
-        <v>81.36</v>
+        <v>419.1687873621491</v>
       </c>
       <c r="P28" t="n">
-        <v>81.36</v>
+        <v>419.1687873621491</v>
       </c>
       <c r="Q28" t="n">
-        <v>81.36</v>
+        <v>81.92</v>
       </c>
       <c r="R28" t="n">
-        <v>81.36</v>
+        <v>81.92</v>
       </c>
       <c r="S28" t="n">
-        <v>81.36</v>
+        <v>81.92</v>
       </c>
       <c r="T28" t="n">
-        <v>96.18567915880486</v>
+        <v>95.75567915880487</v>
       </c>
       <c r="U28" t="n">
-        <v>169.4868717970915</v>
+        <v>168.0668717970915</v>
       </c>
       <c r="V28" t="n">
-        <v>195.0582646830375</v>
+        <v>192.6482646830375</v>
       </c>
       <c r="W28" t="n">
-        <v>193.6715880782802</v>
+        <v>190.2514870681792</v>
       </c>
       <c r="X28" t="n">
-        <v>171.0012391589796</v>
+        <v>190.2514870681792</v>
       </c>
       <c r="Y28" t="n">
-        <v>171.0012391589796</v>
+        <v>190.2514870681792</v>
       </c>
     </row>
     <row r="29">
@@ -6433,22 +6433,22 @@
         <v>1229.164925096351</v>
       </c>
       <c r="C29" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D29" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E29" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F29" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G29" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H29" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I29" t="n">
         <v>81.36</v>
@@ -6460,19 +6460,19 @@
         <v>1182.375479385524</v>
       </c>
       <c r="L29" t="n">
-        <v>2089.404973955146</v>
+        <v>1182.375479385524</v>
       </c>
       <c r="M29" t="n">
-        <v>2600.253802684082</v>
+        <v>1693.224308114459</v>
       </c>
       <c r="N29" t="n">
-        <v>2676.358360925376</v>
+        <v>2306.444627889222</v>
       </c>
       <c r="O29" t="n">
-        <v>3629.400904947332</v>
+        <v>3206.412036092893</v>
       </c>
       <c r="P29" t="n">
-        <v>3629.400904947332</v>
+        <v>4068</v>
       </c>
       <c r="Q29" t="n">
         <v>4068</v>
@@ -6533,16 +6533,16 @@
         <v>89.15487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>435.8613981428639</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K30" t="n">
-        <v>847.8042142372474</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L30" t="n">
-        <v>1341.904675832448</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M30" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N30" t="n">
         <v>1802.941204729126</v>
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>223.1096180158189</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C31" t="n">
-        <v>223.1096180158189</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D31" t="n">
-        <v>161.9619230102073</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E31" t="n">
-        <v>105.4155544880289</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F31" t="n">
-        <v>105.4155544880289</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G31" t="n">
-        <v>85.16921828446326</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H31" t="n">
+        <v>189.862369793817</v>
+      </c>
+      <c r="I31" t="n">
+        <v>237.7452487298999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="K31" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="L31" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="M31" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="N31" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="O31" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="P31" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>425.5789893823512</v>
+      </c>
+      <c r="R31" t="n">
         <v>81.36</v>
       </c>
-      <c r="I31" t="n">
-        <v>129.2428789360829</v>
-      </c>
-      <c r="J31" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="K31" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="L31" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="M31" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="N31" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="O31" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="P31" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>317.0766195885342</v>
-      </c>
-      <c r="R31" t="n">
-        <v>133.4683788568393</v>
-      </c>
       <c r="S31" t="n">
-        <v>133.4683788568393</v>
+        <v>81.36</v>
       </c>
       <c r="T31" t="n">
-        <v>148.2940580156441</v>
+        <v>96.18567915880486</v>
       </c>
       <c r="U31" t="n">
-        <v>221.5952506539307</v>
+        <v>169.4868717970915</v>
       </c>
       <c r="V31" t="n">
-        <v>247.1666435398767</v>
+        <v>195.0582646830375</v>
       </c>
       <c r="W31" t="n">
-        <v>245.7799669351194</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X31" t="n">
-        <v>223.1096180158189</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y31" t="n">
-        <v>223.1096180158189</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="32">
@@ -6667,19 +6667,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C32" t="n">
-        <v>996.8742475204788</v>
+        <v>1002.422926871105</v>
       </c>
       <c r="D32" t="n">
-        <v>809.6629790963881</v>
+        <v>815.2116584470142</v>
       </c>
       <c r="E32" t="n">
-        <v>628.48793908945</v>
+        <v>634.0366184400762</v>
       </c>
       <c r="F32" t="n">
-        <v>446.7812434247916</v>
+        <v>452.3299227754177</v>
       </c>
       <c r="G32" t="n">
         <v>266.2182411146742</v>
@@ -6691,22 +6691,22 @@
         <v>81.36</v>
       </c>
       <c r="J32" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K32" t="n">
-        <v>1182.375479385524</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="L32" t="n">
-        <v>1182.375479385524</v>
+        <v>690.7012485145707</v>
       </c>
       <c r="M32" t="n">
-        <v>1693.224308114459</v>
+        <v>1201.550077243506</v>
       </c>
       <c r="N32" t="n">
-        <v>2306.444627889222</v>
+        <v>1814.770397018269</v>
       </c>
       <c r="O32" t="n">
-        <v>3259.487171911179</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P32" t="n">
         <v>3629.400904947332</v>
@@ -6715,28 +6715,28 @@
         <v>4068</v>
       </c>
       <c r="R32" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S32" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T32" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U32" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V32" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W32" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X32" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y32" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="33">
@@ -6770,25 +6770,25 @@
         <v>89.15487796756496</v>
       </c>
       <c r="J33" t="n">
-        <v>435.8613981428639</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K33" t="n">
-        <v>847.8042142372474</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L33" t="n">
-        <v>1341.904675832448</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M33" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N33" t="n">
-        <v>1854.342732289551</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O33" t="n">
-        <v>2316.13518397327</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P33" t="n">
-        <v>2651.414528442776</v>
+        <v>2600.013000882351</v>
       </c>
       <c r="Q33" t="n">
         <v>2651.414528442776</v>
@@ -6825,52 +6825,52 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="C34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="D34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="E34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="F34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="G34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="H34" t="n">
-        <v>191.2490463985742</v>
+        <v>189.862369793817</v>
       </c>
       <c r="I34" t="n">
-        <v>239.1319253346571</v>
+        <v>237.7452487298999</v>
       </c>
       <c r="J34" t="n">
-        <v>426.9656659871084</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="K34" t="n">
-        <v>426.9656659871084</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="L34" t="n">
-        <v>426.9656659871084</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="M34" t="n">
-        <v>426.9656659871084</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="N34" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="O34" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="P34" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q34" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R34" t="n">
         <v>81.36</v>
@@ -6888,13 +6888,13 @@
         <v>195.0582646830375</v>
       </c>
       <c r="W34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="X34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
       <c r="Y34" t="n">
-        <v>195.0582646830375</v>
+        <v>193.6715880782802</v>
       </c>
     </row>
     <row r="35">
@@ -6919,28 +6919,28 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G35" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H35" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I35" t="n">
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>44.72</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="L35" t="n">
-        <v>598.13</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M35" t="n">
-        <v>1108.978828728935</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N35" t="n">
-        <v>1662.388828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O35" t="n">
         <v>1797.400904947332</v>
@@ -6992,13 +6992,13 @@
         <v>461.5662247731743</v>
       </c>
       <c r="E36" t="n">
-        <v>373.7498342171993</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F36" t="n">
-        <v>373.7498342171993</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G36" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H36" t="n">
         <v>44.72</v>
@@ -7062,28 +7062,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C37" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D37" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E37" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F37" t="n">
-        <v>1161.267639059017</v>
+        <v>1153.55685638681</v>
       </c>
       <c r="G37" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H37" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I37" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J37" t="n">
         <v>1860.696627021627</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U37" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V37" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W37" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X37" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y37" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="38">
@@ -7156,34 +7156,34 @@
         <v>161.6214367433921</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>436.0291130376557</v>
+        <v>64.92117127106515</v>
       </c>
       <c r="K38" t="n">
-        <v>989.4391130376558</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L38" t="n">
-        <v>989.4391130376558</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M38" t="n">
-        <v>989.4391130376558</v>
+        <v>1682.59</v>
       </c>
       <c r="N38" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="O38" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P38" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>55.93203277325181</v>
+        <v>297.950717050992</v>
       </c>
       <c r="C39" t="n">
-        <v>44.72</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="D39" t="n">
-        <v>44.72</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="E39" t="n">
-        <v>44.72</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="F39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I39" t="n">
         <v>44.72</v>
@@ -7265,31 +7265,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q39" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>826.0584179616072</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>708.3170038559392</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>652.400069292794</v>
       </c>
       <c r="U39" t="n">
-        <v>713.1992034391076</v>
+        <v>601.6825341814942</v>
       </c>
       <c r="V39" t="n">
-        <v>648.0369133466629</v>
+        <v>536.5202440890496</v>
       </c>
       <c r="W39" t="n">
-        <v>564.8317184882503</v>
+        <v>453.3150492306369</v>
       </c>
       <c r="X39" t="n">
-        <v>494.2632948060407</v>
+        <v>382.7466255484273</v>
       </c>
       <c r="Y39" t="n">
-        <v>90.8376455473191</v>
+        <v>332.8563298250593</v>
       </c>
     </row>
     <row r="40">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D41" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H41" t="n">
         <v>44.72</v>
@@ -7402,25 +7402,25 @@
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>179.7320762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L41" t="n">
-        <v>733.1420762183976</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M41" t="n">
-        <v>1243.990904947333</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N41" t="n">
-        <v>1243.990904947333</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O41" t="n">
-        <v>1243.990904947333</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7429,25 +7429,25 @@
         <v>2236</v>
       </c>
       <c r="S41" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X41" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="42">
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>119.2429040110725</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C42" t="n">
         <v>44.72</v>
@@ -7508,25 +7508,25 @@
         <v>647.3506049216877</v>
       </c>
       <c r="S42" t="n">
-        <v>529.6091908160197</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T42" t="n">
-        <v>473.6922562528744</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U42" t="n">
-        <v>422.9747211415747</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V42" t="n">
-        <v>357.8124310491301</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W42" t="n">
-        <v>274.6072361907174</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X42" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y42" t="n">
-        <v>154.1485167851397</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="43">
@@ -7536,31 +7536,31 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C43" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D43" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E43" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F43" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G43" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H43" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I43" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J43" t="n">
-        <v>1860.696627021627</v>
+        <v>1868.407409693835</v>
       </c>
       <c r="K43" t="n">
         <v>1921.561060958496</v>
@@ -7590,22 +7590,22 @@
         <v>44.72</v>
       </c>
       <c r="T43" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U43" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V43" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W43" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X43" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y43" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>433.4059340138206</v>
+        <v>425.3251259330126</v>
       </c>
       <c r="C44" t="n">
-        <v>332.9265620512004</v>
+        <v>323.8356529602914</v>
       </c>
       <c r="D44" t="n">
-        <v>271.977919889736</v>
+        <v>261.876909788726</v>
       </c>
       <c r="E44" t="n">
-        <v>217.0655061454243</v>
+        <v>205.9543950343132</v>
       </c>
       <c r="F44" t="n">
-        <v>157.615990899539</v>
+        <v>149.50022462218</v>
       </c>
       <c r="G44" t="n">
-        <v>103.3156148520479</v>
+        <v>104.3257158621489</v>
       </c>
       <c r="H44" t="n">
         <v>44.72</v>
@@ -7639,25 +7639,25 @@
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>64.9211712710653</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="K44" t="n">
-        <v>64.9211712710653</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="L44" t="n">
-        <v>64.9211712710653</v>
+        <v>179.7320762183977</v>
       </c>
       <c r="M44" t="n">
-        <v>575.7700000000003</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N44" t="n">
-        <v>1129.18</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O44" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q44" t="n">
         <v>2236</v>
@@ -7666,25 +7666,25 @@
         <v>2236</v>
       </c>
       <c r="S44" t="n">
-        <v>2089.688719391593</v>
+        <v>2088.678618381492</v>
       </c>
       <c r="T44" t="n">
-        <v>1850.622475221327</v>
+        <v>1848.602273201124</v>
       </c>
       <c r="U44" t="n">
-        <v>1548.378741333841</v>
+        <v>1545.348438303538</v>
       </c>
       <c r="V44" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.660535104726</v>
       </c>
       <c r="W44" t="n">
-        <v>974.4145997704354</v>
+        <v>969.3640947199306</v>
       </c>
       <c r="X44" t="n">
-        <v>729.6854750626902</v>
+        <v>723.6248690020843</v>
       </c>
       <c r="Y44" t="n">
-        <v>566.7385733628857</v>
+        <v>559.6678662921788</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>472.7782575464261</v>
+        <v>56.94213378335282</v>
       </c>
       <c r="C45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G45" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H45" t="n">
         <v>44.72</v>
@@ -7742,28 +7742,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>474.3791276590071</v>
       </c>
       <c r="T45" t="n">
-        <v>827.2276097882281</v>
+        <v>417.4520920857609</v>
       </c>
       <c r="U45" t="n">
-        <v>776.5100746769283</v>
+        <v>365.7244559643601</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>299.5520648618145</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>215.3367689933008</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438614</v>
+        <v>143.7582443009902</v>
       </c>
       <c r="Y45" t="n">
-        <v>507.6838703204934</v>
+        <v>92.85784756752112</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.0458296400257</v>
+        <v>870.8266123122328</v>
       </c>
       <c r="C46" t="n">
-        <v>946.5478354584615</v>
+        <v>946.3386181306686</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.366979583462</v>
+        <v>1009.167762255669</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.695883794875</v>
+        <v>1076.506666467082</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.55685638681</v>
+        <v>1150.377639059017</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.463422273695</v>
+        <v>1253.294204945902</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1372.3207901053</v>
       </c>
       <c r="I46" t="n">
-        <v>1549.112886369176</v>
+        <v>1542.963669041383</v>
       </c>
       <c r="J46" t="n">
-        <v>1860.696627021627</v>
+        <v>1853.557409693834</v>
       </c>
       <c r="K46" t="n">
-        <v>1921.561060958496</v>
+        <v>1913.431843630703</v>
       </c>
       <c r="L46" t="n">
-        <v>1847.270527465789</v>
+        <v>1838.131209127896</v>
       </c>
       <c r="M46" t="n">
-        <v>1674.915364432911</v>
+        <v>1664.765945084916</v>
       </c>
       <c r="N46" t="n">
-        <v>1451.496096481714</v>
+        <v>1440.336576123618</v>
       </c>
       <c r="O46" t="n">
-        <v>1158.116738826143</v>
+        <v>1145.947117457946</v>
       </c>
       <c r="P46" t="n">
-        <v>817.2602768783884</v>
+        <v>804.0805545000901</v>
       </c>
       <c r="Q46" t="n">
-        <v>437.6246542262692</v>
+        <v>426.1362908900516</v>
       </c>
       <c r="R46" t="n">
-        <v>57.21846434631862</v>
+        <v>44.72</v>
       </c>
       <c r="S46" t="n">
         <v>44.72</v>
       </c>
       <c r="T46" t="n">
-        <v>175.5848964865977</v>
+        <v>182.3056791588048</v>
       </c>
       <c r="U46" t="n">
-        <v>372.6360891248843</v>
+        <v>378.3668717970914</v>
       </c>
       <c r="V46" t="n">
-        <v>521.9574820108303</v>
+        <v>526.6982646830375</v>
       </c>
       <c r="W46" t="n">
-        <v>644.3484002705077</v>
+        <v>648.0991829427148</v>
       </c>
       <c r="X46" t="n">
-        <v>745.8791912947012</v>
+        <v>748.6399739669083</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.7884919737335</v>
+        <v>809.5592746459406</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7973,19 +7973,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>921.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>477.2489580698352</v>
+        <v>854.2489580698352</v>
       </c>
       <c r="O2" t="n">
-        <v>455.2478695740924</v>
+        <v>447.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>369.7315044851258</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
-        <v>557.8226843274854</v>
+        <v>534.5903610951621</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8207,10 +8207,10 @@
         <v>385</v>
       </c>
       <c r="L5" t="n">
-        <v>385</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N5" t="n">
         <v>862.2489580698352</v>
@@ -8222,7 +8222,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>542.2671287719298</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8453,13 +8453,13 @@
         <v>862.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409245</v>
+        <v>439.6923140185369</v>
       </c>
       <c r="P8" t="n">
-        <v>369.7315044851259</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>172.8226843274854</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,13 +8675,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K11" t="n">
-        <v>174.3339442569695</v>
+        <v>615.4962106207786</v>
       </c>
       <c r="L11" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8693,7 +8693,7 @@
         <v>1032.917105959907</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,10 +8927,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P14" t="n">
-        <v>815.6768535014329</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9149,10 +9149,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>569.5956745980359</v>
       </c>
       <c r="L17" t="n">
         <v>916.1914086561842</v>
@@ -9164,10 +9164,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P17" t="n">
-        <v>420.4151231603661</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9395,13 +9395,13 @@
         <v>916.1914086561842</v>
       </c>
       <c r="M20" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>852.9690954914502</v>
+        <v>336.9601775834349</v>
       </c>
       <c r="P20" t="n">
         <v>870.5779326741233</v>
@@ -9629,16 +9629,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N23" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>956.3746420023875</v>
+        <v>1032.917105959907</v>
       </c>
       <c r="P23" t="n">
         <v>870.5779326741233</v>
@@ -9866,7 +9866,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,10 +9875,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>933.4053216358654</v>
+        <v>1007.02302937578</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q26" t="n">
         <v>172.8226843274854</v>
@@ -10103,22 +10103,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>554.1222492226578</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>1032.917105959907</v>
+        <v>979.305857658608</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,10 +10334,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230994</v>
+        <v>615.4962106207786</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -10352,7 +10352,7 @@
         <v>1032.917105959907</v>
       </c>
       <c r="P32" t="n">
-        <v>373.9372954307356</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10571,13 +10571,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
@@ -10586,7 +10586,7 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
-        <v>206.6237041381302</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
         <v>0.2870600406814136</v>
@@ -10808,28 +10808,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>55.44822975121676</v>
       </c>
       <c r="K38" t="n">
         <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>734.3719802008219</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,28 +11045,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P41" t="n">
-        <v>559.2870600406815</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,7 +11282,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>55.44822975121691</v>
+        <v>171.4188408091284</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -11300,10 +11300,10 @@
         <v>629.2478695740924</v>
       </c>
       <c r="P44" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22563,7 +22563,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.340208614583844</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -22706,13 +22706,13 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5911706460559</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>32.63757064605582</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -22952,7 +22952,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.59117064605573</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23423,13 +23423,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23633,7 +23633,7 @@
         <v>49.38285596774193</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -23645,10 +23645,10 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M16" t="n">
         <v>295.6316114025499</v>
@@ -23666,7 +23666,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>441.5647934543659</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S16" t="n">
         <v>137.3734797028554</v>
@@ -23681,7 +23681,7 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>22.44364543010755</v>
@@ -23873,7 +23873,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H19" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -23897,10 +23897,10 @@
         <v>415.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>117.8999717381312</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>500.839266425598</v>
+        <v>160.0624669370703</v>
       </c>
       <c r="R19" t="n">
         <v>501.6021279811511</v>
@@ -24119,13 +24119,13 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>17.00277587645562</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L22" t="n">
         <v>198.5476281577792</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>295.6316114025499</v>
       </c>
       <c r="N22" t="n">
         <v>346.1850752716849</v>
@@ -24140,7 +24140,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S22" t="n">
         <v>137.3734797028554</v>
@@ -24155,7 +24155,7 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>22.44364543010755</v>
@@ -24329,7 +24329,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C25" t="n">
         <v>47.72524664804467</v>
@@ -24341,13 +24341,13 @@
         <v>55.98090483695654</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G25" t="n">
         <v>20.04387284153003</v>
       </c>
       <c r="H25" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -24377,7 +24377,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>290.9945041259329</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S25" t="n">
         <v>137.3734797028554</v>
@@ -24395,7 +24395,7 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y25" t="n">
         <v>62.46535284946236</v>
@@ -24566,25 +24566,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62.11380033707866</v>
+        <v>63.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>47.72524664804467</v>
+        <v>48.72524664804467</v>
       </c>
       <c r="D28" t="n">
-        <v>60.53621805555548</v>
+        <v>61.53621805555548</v>
       </c>
       <c r="E28" t="n">
-        <v>16.61893403730862</v>
+        <v>56.98090483695654</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>50.38285596774193</v>
       </c>
       <c r="G28" t="n">
-        <v>20.04387284153003</v>
+        <v>21.04387284153003</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24593,31 +24593,31 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>63.52077380114304</v>
+        <v>64.52077380114304</v>
       </c>
       <c r="L28" t="n">
-        <v>198.5476281577792</v>
+        <v>199.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>295.6316114025499</v>
+        <v>296.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>346.1850752716849</v>
+        <v>347.1850752716849</v>
       </c>
       <c r="O28" t="n">
-        <v>182.0861106863661</v>
+        <v>416.445564079015</v>
       </c>
       <c r="P28" t="n">
-        <v>462.4478973282775</v>
+        <v>463.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>500.839266425598</v>
+        <v>167.9629669370703</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>502.6021279811511</v>
       </c>
       <c r="S28" t="n">
-        <v>137.3734797028554</v>
+        <v>138.3734797028554</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24632,10 +24632,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>23.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>62.46535284946236</v>
+        <v>63.46535284946236</v>
       </c>
     </row>
     <row r="29">
@@ -24809,16 +24809,16 @@
         <v>47.72524664804467</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>55.98090483695654</v>
       </c>
       <c r="F31" t="n">
         <v>49.38285596774193</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -24851,7 +24851,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>319.829969656773</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -24869,7 +24869,7 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y31" t="n">
         <v>62.46535284946236</v>
@@ -25076,7 +25076,7 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>4.035465944447594</v>
+        <v>346.1850752716849</v>
       </c>
       <c r="O34" t="n">
         <v>415.445564079015</v>
@@ -25088,7 +25088,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S34" t="n">
         <v>137.3734797028554</v>
@@ -25103,7 +25103,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>22.44364543010755</v>
@@ -25845,7 +25845,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>10.0346086145854</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -26033,13 +26033,13 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.674445451659835</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>13.37347970285543</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1157099.39426644</v>
+        <v>1155906.203730374</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2259020.889973892</v>
+        <v>2258205.920043887</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3360942.385681347</v>
+        <v>3360127.415751341</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4430585.044896968</v>
+        <v>4429770.074966962</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5470348.276233801</v>
+        <v>5469533.306303795</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6510111.507570631</v>
+        <v>6509296.537640627</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7549874.738907457</v>
+        <v>7549059.768977453</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8589637.970244287</v>
+        <v>8588823.00031428</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9629401.201581115</v>
+        <v>9628415.264181411</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10669164.43291794</v>
+        <v>10667847.55248794</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11708927.66425477</v>
+        <v>11707610.78382476</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12789229.44484883</v>
+        <v>12787912.56441882</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13891184.35513986</v>
+        <v>13889867.47470985</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14993139.26543088</v>
+        <v>14991822.38500088</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16095094.17572191</v>
+        <v>16092741.37837365</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1101921.495707453</v>
+        <v>1101106.525777448</v>
       </c>
       <c r="C2" t="n">
         <v>1101921.495707453</v>
@@ -26281,10 +26281,10 @@
         <v>1039763.231336833</v>
       </c>
       <c r="F2" t="n">
+        <v>1039763.231336833</v>
+      </c>
+      <c r="G2" t="n">
         <v>1039763.231336832</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1039763.231336833</v>
       </c>
       <c r="H2" t="n">
         <v>1039763.231336833</v>
@@ -26293,7 +26293,7 @@
         <v>1039763.231336833</v>
       </c>
       <c r="J2" t="n">
-        <v>1039763.231336832</v>
+        <v>1039261.320836833</v>
       </c>
       <c r="K2" t="n">
         <v>1039763.231336833</v>
@@ -26308,10 +26308,10 @@
         <v>1101954.910291021</v>
       </c>
       <c r="O2" t="n">
-        <v>1101954.91029102</v>
+        <v>1101954.910291021</v>
       </c>
       <c r="P2" t="n">
-        <v>1101954.910291021</v>
+        <v>1100918.99337277</v>
       </c>
     </row>
     <row r="3">
@@ -26321,10 +26321,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>135520</v>
+        <v>132704</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>2816</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>315520</v>
+        <v>314368</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26360,7 +26360,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>180000</v>
+        <v>179200</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572894.2778066027</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416947</v>
       </c>
       <c r="E4" t="n">
-        <v>445852.6895118617</v>
+        <v>448189.3974235593</v>
       </c>
       <c r="F4" t="n">
-        <v>444399.1387482317</v>
+        <v>446735.8466599294</v>
       </c>
       <c r="G4" t="n">
-        <v>442943.5821390834</v>
+        <v>445280.290050781</v>
       </c>
       <c r="H4" t="n">
-        <v>441486.0053004215</v>
+        <v>443822.7132121191</v>
       </c>
       <c r="I4" t="n">
-        <v>440026.3936608352</v>
+        <v>442363.1015725328</v>
       </c>
       <c r="J4" t="n">
-        <v>438564.7324579426</v>
+        <v>439748.2013963978</v>
       </c>
       <c r="K4" t="n">
-        <v>437101.0067347542</v>
+        <v>439437.7146464518</v>
       </c>
       <c r="L4" t="n">
-        <v>435635.201335937</v>
+        <v>437971.9092476346</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.6773203551</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>522671.0542953383</v>
       </c>
     </row>
     <row r="5">
@@ -26425,7 +26425,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57035.6</v>
+        <v>56549.2</v>
       </c>
       <c r="C5" t="n">
         <v>57035.6</v>
@@ -26449,7 +26449,7 @@
         <v>80749.125</v>
       </c>
       <c r="J5" t="n">
-        <v>80749.125</v>
+        <v>81090.656</v>
       </c>
       <c r="K5" t="n">
         <v>80749.125</v>
@@ -26467,7 +26467,7 @@
         <v>63411.35</v>
       </c>
       <c r="P5" t="n">
-        <v>63411.35</v>
+        <v>63327.281</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>338451.7708079441</v>
+        <v>338959.0479708448</v>
       </c>
       <c r="C6" t="n">
-        <v>476029.7509417586</v>
+        <v>471697.8952534428</v>
       </c>
       <c r="D6" t="n">
-        <v>478090.5228540745</v>
+        <v>476574.6671657586</v>
       </c>
       <c r="E6" t="n">
-        <v>110697.4168249708</v>
+        <v>108360.7089132732</v>
       </c>
       <c r="F6" t="n">
-        <v>514614.9675886007</v>
+        <v>512278.2596769031</v>
       </c>
       <c r="G6" t="n">
-        <v>516070.5241977492</v>
+        <v>513733.8162860514</v>
       </c>
       <c r="H6" t="n">
-        <v>517528.1010364111</v>
+        <v>515191.3931247133</v>
       </c>
       <c r="I6" t="n">
-        <v>518987.7126759975</v>
+        <v>516651.0047642997</v>
       </c>
       <c r="J6" t="n">
-        <v>204929.3738788898</v>
+        <v>204054.4634404349</v>
       </c>
       <c r="K6" t="n">
-        <v>521913.0996020784</v>
+        <v>518424.3916903806</v>
       </c>
       <c r="L6" t="n">
-        <v>523378.9050008955</v>
+        <v>521042.197089198</v>
       </c>
       <c r="M6" t="n">
-        <v>349820.8357489201</v>
+        <v>348078.9859358124</v>
       </c>
       <c r="N6" t="n">
-        <v>513033.7327837734</v>
+        <v>511291.8829706657</v>
       </c>
       <c r="O6" t="n">
-        <v>335001.4720415112</v>
+        <v>334059.6222284037</v>
       </c>
       <c r="P6" t="n">
-        <v>516972.0748925217</v>
+        <v>514920.6580774313</v>
       </c>
     </row>
   </sheetData>
@@ -26779,7 +26779,7 @@
         <v>225</v>
       </c>
       <c r="J2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K2" t="n">
         <v>225</v>
@@ -26797,7 +26797,7 @@
         <v>350</v>
       </c>
       <c r="P2" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3">
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C4" t="n">
         <v>385</v>
@@ -26883,7 +26883,7 @@
         <v>1017</v>
       </c>
       <c r="J4" t="n">
-        <v>1017</v>
+        <v>1024</v>
       </c>
       <c r="K4" t="n">
         <v>1017</v>
@@ -26987,7 +26987,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -26996,13 +26996,13 @@
         <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>125</v>
@@ -27011,7 +27011,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
@@ -27039,22 +27039,22 @@
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,10 +27100,10 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27228,10 +27228,10 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>121.3749682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>250.878598828296</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27524,13 +27524,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>204.2843561227032</v>
       </c>
       <c r="G3" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27557,13 +27557,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>99.03700384580264</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27597,7 +27597,7 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
         <v>400</v>
@@ -27606,7 +27606,7 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
@@ -27615,10 +27615,10 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
-        <v>152.6602193074314</v>
+        <v>400</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>300.9285493262165</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,7 +27642,7 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
         <v>210.0245665062577</v>
@@ -27651,16 +27651,16 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27767,7 +27767,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>77.30592606523138</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27797,7 +27797,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>162.2737972923793</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27809,10 +27809,10 @@
         <v>400</v>
       </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>260.0384932613611</v>
       </c>
       <c r="W6" t="n">
-        <v>400</v>
+        <v>47.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>34.86273944538755</v>
@@ -27834,28 +27834,28 @@
         <v>400</v>
       </c>
       <c r="D7" t="n">
-        <v>383.9690176440507</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>328.0111212709322</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27882,19 +27882,19 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X7" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27922,13 +27922,13 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27998,13 +27998,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>139.8182410159025</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>20.73541136457013</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28040,7 +28040,7 @@
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>20.35776521751382</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28074,16 +28074,16 @@
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>372.2356904372913</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>245.04387284153</v>
       </c>
       <c r="H10" t="n">
-        <v>324.2765420337191</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
         <v>176.6334556201183</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
         <v>400</v>
@@ -28128,7 +28128,7 @@
         <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>226.3728098387097</v>
+        <v>400</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28162,7 +28162,7 @@
         <v>225</v>
       </c>
       <c r="H11" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
       <c r="I11" t="n">
         <v>150.0811596826846</v>
@@ -28195,7 +28195,7 @@
         <v>225</v>
       </c>
       <c r="S11" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="T11" t="n">
         <v>225</v>
@@ -28250,7 +28250,7 @@
         <v>225</v>
       </c>
       <c r="K12" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="L12" t="n">
         <v>225</v>
@@ -28265,7 +28265,7 @@
         <v>225</v>
       </c>
       <c r="P12" t="n">
-        <v>225</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q12" t="n">
         <v>225</v>
@@ -28390,7 +28390,7 @@
         <v>225</v>
       </c>
       <c r="E14" t="n">
-        <v>219.5068074428801</v>
+        <v>225</v>
       </c>
       <c r="F14" t="n">
         <v>225</v>
@@ -28402,7 +28402,7 @@
         <v>225</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>144.5879671255647</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28484,7 +28484,7 @@
         <v>225</v>
       </c>
       <c r="J15" t="n">
-        <v>225</v>
+        <v>19.11687125883914</v>
       </c>
       <c r="K15" t="n">
         <v>225</v>
@@ -28493,7 +28493,7 @@
         <v>225</v>
       </c>
       <c r="M15" t="n">
-        <v>19.11687125883903</v>
+        <v>225</v>
       </c>
       <c r="N15" t="n">
         <v>225</v>
@@ -28639,7 +28639,7 @@
         <v>225</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>144.5879671255647</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28675,7 +28675,7 @@
         <v>225</v>
       </c>
       <c r="U17" t="n">
-        <v>219.50680744288</v>
+        <v>225</v>
       </c>
       <c r="V17" t="n">
         <v>225</v>
@@ -28724,13 +28724,13 @@
         <v>225</v>
       </c>
       <c r="K18" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="L18" t="n">
         <v>225</v>
       </c>
       <c r="M18" t="n">
-        <v>19.11687125883903</v>
+        <v>225</v>
       </c>
       <c r="N18" t="n">
         <v>225</v>
@@ -28867,7 +28867,7 @@
         <v>225</v>
       </c>
       <c r="F20" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
       <c r="G20" t="n">
         <v>225</v>
@@ -28918,7 +28918,7 @@
         <v>225</v>
       </c>
       <c r="W20" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="X20" t="n">
         <v>225</v>
@@ -28955,13 +28955,13 @@
         <v>225</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J21" t="n">
-        <v>225</v>
+        <v>19.11687125883914</v>
       </c>
       <c r="K21" t="n">
-        <v>26.99048536749061</v>
+        <v>225</v>
       </c>
       <c r="L21" t="n">
         <v>225</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S23" t="n">
         <v>225</v>
@@ -29149,7 +29149,7 @@
         <v>225</v>
       </c>
       <c r="U23" t="n">
-        <v>225</v>
+        <v>219.50680744288</v>
       </c>
       <c r="V23" t="n">
         <v>225</v>
@@ -29198,7 +29198,7 @@
         <v>225</v>
       </c>
       <c r="K24" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="L24" t="n">
         <v>225</v>
@@ -29207,7 +29207,7 @@
         <v>225</v>
       </c>
       <c r="N24" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="O24" t="n">
         <v>225</v>
@@ -29329,28 +29329,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I26" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29377,28 +29377,28 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X26" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y26" t="n">
-        <v>225</v>
+        <v>206.3412074428803</v>
       </c>
     </row>
     <row r="27">
@@ -29408,76 +29408,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>224</v>
       </c>
       <c r="J27" t="n">
-        <v>26.99048536749061</v>
+        <v>224</v>
       </c>
       <c r="K27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O27" t="n">
-        <v>225</v>
+        <v>42.42143201794514</v>
       </c>
       <c r="P27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y27" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28">
@@ -29487,76 +29487,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="O28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="S28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="W28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Y28" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="29">
@@ -29569,7 +29569,7 @@
         <v>225</v>
       </c>
       <c r="C29" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="D29" t="n">
         <v>225</v>
@@ -29587,7 +29587,7 @@
         <v>225</v>
       </c>
       <c r="I29" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29669,7 +29669,7 @@
         <v>225</v>
       </c>
       <c r="J30" t="n">
-        <v>225</v>
+        <v>19.11687125883914</v>
       </c>
       <c r="K30" t="n">
         <v>225</v>
@@ -29681,7 +29681,7 @@
         <v>225</v>
       </c>
       <c r="N30" t="n">
-        <v>19.11687125883913</v>
+        <v>225</v>
       </c>
       <c r="O30" t="n">
         <v>225</v>
@@ -29818,7 +29818,7 @@
         <v>225</v>
       </c>
       <c r="G32" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="H32" t="n">
         <v>225</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S32" t="n">
         <v>225</v>
@@ -29906,7 +29906,7 @@
         <v>225</v>
       </c>
       <c r="J33" t="n">
-        <v>225</v>
+        <v>19.11687125883914</v>
       </c>
       <c r="K33" t="n">
         <v>225</v>
@@ -29918,7 +29918,7 @@
         <v>225</v>
       </c>
       <c r="N33" t="n">
-        <v>71.0376061683595</v>
+        <v>225</v>
       </c>
       <c r="O33" t="n">
         <v>225</v>
@@ -29927,7 +29927,7 @@
         <v>225</v>
       </c>
       <c r="Q33" t="n">
-        <v>173.0792650904796</v>
+        <v>225</v>
       </c>
       <c r="R33" t="n">
         <v>225</v>
@@ -30055,13 +30055,13 @@
         <v>350</v>
       </c>
       <c r="G35" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="H35" t="n">
         <v>350</v>
       </c>
       <c r="I35" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -30128,16 +30128,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>255.7338705714974</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>245.2298605360059</v>
       </c>
       <c r="H36" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>217.1263858913485</v>
@@ -30222,7 +30222,7 @@
         <v>350</v>
       </c>
       <c r="J37" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="K37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30292,13 +30292,13 @@
         <v>350</v>
       </c>
       <c r="G38" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="H38" t="n">
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30368,7 +30368,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>317.1641307942626</v>
       </c>
       <c r="G39" t="n">
         <v>325.7395358750273</v>
@@ -30377,7 +30377,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>350</v>
@@ -30413,7 +30413,7 @@
         <v>350</v>
       </c>
       <c r="U39" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="V39" t="n">
         <v>350</v>
@@ -30425,7 +30425,7 @@
         <v>350</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40">
@@ -30532,7 +30532,7 @@
         <v>350</v>
       </c>
       <c r="H41" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I41" t="n">
         <v>150.0811596826846</v>
@@ -30565,7 +30565,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S41" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T41" t="n">
         <v>350</v>
@@ -30596,7 +30596,7 @@
         <v>350</v>
       </c>
       <c r="C42" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="D42" t="n">
         <v>347.9376868977026</v>
@@ -30644,7 +30644,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T42" t="n">
         <v>350</v>
@@ -30699,7 +30699,7 @@
         <v>350</v>
       </c>
       <c r="K43" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="L43" t="n">
         <v>350</v>
@@ -30726,7 +30726,7 @@
         <v>350</v>
       </c>
       <c r="T43" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U43" t="n">
         <v>350</v>
@@ -30751,25 +30751,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F44" t="n">
-        <v>346.0346086145855</v>
+        <v>349</v>
       </c>
       <c r="G44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I44" t="n">
         <v>150.0811596826846</v>
@@ -30802,25 +30802,25 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="T44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="U44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="W44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y44" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="45">
@@ -30830,10 +30830,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C45" t="n">
-        <v>269.4903246609786</v>
+        <v>349</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
@@ -30848,7 +30848,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
         <v>217.1263858913485</v>
@@ -30878,28 +30878,28 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>350</v>
+        <v>295.3222374745575</v>
       </c>
       <c r="T45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="U45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="W45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y45" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46">
@@ -30909,76 +30909,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="M46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="R46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="S46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="T46" t="n">
-        <v>342.2113306341342</v>
+        <v>349</v>
       </c>
       <c r="U46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="V46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="W46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Y46" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34752,22 +34752,22 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>377</v>
       </c>
       <c r="O2" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="P2" t="n">
-        <v>369.4444444444443</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>385</v>
+        <v>361.7676767676766</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.607692654649116e-12</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -34883,7 +34883,7 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
         <v>119.0190951630435</v>
@@ -34892,7 +34892,7 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
         <v>171.2288738983814</v>
@@ -34901,10 +34901,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>117.3912704715236</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
-        <v>111.479226198857</v>
+        <v>12.4077755250735</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,7 +34928,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -34937,16 +34937,16 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34986,10 +34986,10 @@
         <v>385</v>
       </c>
       <c r="L5" t="n">
+        <v>369.4444444444445</v>
+      </c>
+      <c r="M5" t="n">
         <v>385</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>385</v>
@@ -35001,7 +35001,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35120,28 +35120,28 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
-        <v>98.43279958849526</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>53.62826530319025</v>
       </c>
       <c r="G7" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35168,19 +35168,19 @@
         <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
         <v>249.0416087255421</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35217,7 +35217,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -35232,13 +35232,13 @@
         <v>385</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="P8" t="n">
-        <v>369.4444444444445</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35360,16 +35360,16 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>91.25478560033478</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>95.50541593210053</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>189.9754334937423</v>
@@ -35414,7 +35414,7 @@
         <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35454,13 +35454,13 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>174.3339442569695</v>
+        <v>615.4962106207786</v>
       </c>
       <c r="L11" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35472,7 +35472,7 @@
         <v>962.6692363858147</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35536,7 +35536,7 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>210.2207258996305</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
         <v>499.091375348687</v>
@@ -35551,7 +35551,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q12" t="n">
         <v>51.92073490952041</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,10 +35706,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P14" t="n">
-        <v>815.3897934607513</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35770,7 +35770,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J15" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K15" t="n">
         <v>416.1038546407913</v>
@@ -35779,7 +35779,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M15" t="n">
-        <v>106.0669134233433</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N15" t="n">
         <v>359.6265501086548</v>
@@ -35928,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230996</v>
+        <v>569.5956745980359</v>
       </c>
       <c r="L17" t="n">
         <v>916.1914086561842</v>
@@ -35943,10 +35943,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P17" t="n">
-        <v>420.1280631196846</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36010,13 +36010,13 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>416.1038546407913</v>
+        <v>210.2207258996305</v>
       </c>
       <c r="L18" t="n">
         <v>499.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>106.0669134233433</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N18" t="n">
         <v>359.6265501086548</v>
@@ -36174,13 +36174,13 @@
         <v>916.1914086561842</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>782.7212259173577</v>
+        <v>266.7123080093424</v>
       </c>
       <c r="P20" t="n">
         <v>870.2908726334418</v>
@@ -36241,13 +36241,13 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J21" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K21" t="n">
-        <v>218.0943400082819</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L21" t="n">
         <v>499.091375348687</v>
@@ -36408,16 +36408,16 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>220.2344802797121</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>886.126772428295</v>
+        <v>962.6692363858147</v>
       </c>
       <c r="P23" t="n">
         <v>870.2908726334418</v>
@@ -36484,7 +36484,7 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>416.1038546407913</v>
+        <v>210.2207258996305</v>
       </c>
       <c r="L24" t="n">
         <v>499.091375348687</v>
@@ -36493,7 +36493,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N24" t="n">
-        <v>153.743421367494</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O24" t="n">
         <v>466.4570219027464</v>
@@ -36642,10 +36642,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L26" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,10 +36654,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>863.157452061773</v>
+        <v>936.7751598016873</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36715,31 +36715,31 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>6.873614108651466</v>
       </c>
       <c r="J27" t="n">
-        <v>152.1990916051663</v>
+        <v>349.2086062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>416.1038546407913</v>
+        <v>415.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>499.091375348687</v>
+        <v>498.091375348687</v>
       </c>
       <c r="M27" t="n">
-        <v>311.9500421645043</v>
+        <v>310.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>359.6265501086548</v>
+        <v>358.6265501086548</v>
       </c>
       <c r="O27" t="n">
-        <v>466.4570219027464</v>
+        <v>283.8784539206915</v>
       </c>
       <c r="P27" t="n">
-        <v>338.6660045146532</v>
+        <v>337.6660045146532</v>
       </c>
       <c r="Q27" t="n">
-        <v>51.92073490952041</v>
+        <v>50.92073490952041</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36794,10 +36794,10 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>48.36654437988173</v>
+        <v>47.36654437988173</v>
       </c>
       <c r="J28" t="n">
-        <v>189.7310511640922</v>
+        <v>188.7310511640922</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -36827,13 +36827,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>14.97543349374229</v>
+        <v>13.97543349374229</v>
       </c>
       <c r="U28" t="n">
-        <v>74.04160872554206</v>
+        <v>73.04160872554206</v>
       </c>
       <c r="V28" t="n">
-        <v>25.82968978378381</v>
+        <v>24.82968978378381</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
@@ -36882,22 +36882,22 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L29" t="n">
-        <v>916.1914086561842</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>76.87329115282263</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>962.6692363858147</v>
+        <v>909.0579880845156</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36955,7 +36955,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K30" t="n">
         <v>416.1038546407913</v>
@@ -36967,7 +36967,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N30" t="n">
-        <v>153.743421367494</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O30" t="n">
         <v>466.4570219027464</v>
@@ -37113,10 +37113,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230996</v>
+        <v>615.4962106207786</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -37131,7 +37131,7 @@
         <v>962.6692363858147</v>
       </c>
       <c r="P32" t="n">
-        <v>373.6502353900542</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
@@ -37192,7 +37192,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J33" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K33" t="n">
         <v>416.1038546407913</v>
@@ -37204,7 +37204,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N33" t="n">
-        <v>205.6641562770143</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O33" t="n">
         <v>466.4570219027464</v>
@@ -37213,7 +37213,7 @@
         <v>338.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>51.92073490952041</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37350,13 +37350,13 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>300.1141042229715</v>
       </c>
       <c r="L35" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>516.0089179080152</v>
@@ -37365,7 +37365,7 @@
         <v>559</v>
       </c>
       <c r="O35" t="n">
-        <v>136.3758345640378</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -37508,7 +37508,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J37" t="n">
-        <v>306.9423817982264</v>
+        <v>314.7310511640923</v>
       </c>
       <c r="K37" t="n">
         <v>61.47922619885696</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>395.2617303410664</v>
+        <v>20.40522350612643</v>
       </c>
       <c r="K38" t="n">
         <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>257.1230221309867</v>
+        <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37824,28 +37824,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P41" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37985,7 +37985,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K43" t="n">
-        <v>61.47922619885696</v>
+        <v>53.69055683299113</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U43" t="n">
         <v>199.0416087255421</v>
@@ -38061,7 +38061,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>20.40522350612659</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>559</v>
       </c>
       <c r="P44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38195,34 +38195,34 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>62.88619966292134</v>
+        <v>61.88619966292134</v>
       </c>
       <c r="C46" t="n">
-        <v>77.27475335195533</v>
+        <v>76.27475335195533</v>
       </c>
       <c r="D46" t="n">
-        <v>64.46378194444452</v>
+        <v>63.46378194444452</v>
       </c>
       <c r="E46" t="n">
-        <v>69.01909516304346</v>
+        <v>68.01909516304346</v>
       </c>
       <c r="F46" t="n">
-        <v>75.61714403225807</v>
+        <v>74.61714403225807</v>
       </c>
       <c r="G46" t="n">
-        <v>104.95612715847</v>
+        <v>103.95612715847</v>
       </c>
       <c r="H46" t="n">
-        <v>121.2288738983814</v>
+        <v>120.2288738983814</v>
       </c>
       <c r="I46" t="n">
-        <v>173.3665443798817</v>
+        <v>172.3665443798817</v>
       </c>
       <c r="J46" t="n">
-        <v>314.7310511640923</v>
+        <v>313.7310511640923</v>
       </c>
       <c r="K46" t="n">
-        <v>61.47922619885696</v>
+        <v>60.47922619885696</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,22 +38249,22 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>132.1867641278765</v>
+        <v>138.9754334937423</v>
       </c>
       <c r="U46" t="n">
-        <v>199.0416087255421</v>
+        <v>198.0416087255421</v>
       </c>
       <c r="V46" t="n">
-        <v>150.8296897837838</v>
+        <v>149.8296897837838</v>
       </c>
       <c r="W46" t="n">
-        <v>123.6271901612903</v>
+        <v>122.6271901612903</v>
       </c>
       <c r="X46" t="n">
-        <v>102.5563545698924</v>
+        <v>101.5563545698924</v>
       </c>
       <c r="Y46" t="n">
-        <v>62.53464715053764</v>
+        <v>61.53464715053764</v>
       </c>
     </row>
   </sheetData>
